--- a/exports/trend_1d/BHEL_full_report.xlsx
+++ b/exports/trend_1d/BHEL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:U83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>10.23</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42040</v>
+        <v>42041</v>
       </c>
       <c r="H2" t="n">
-        <v>184.57</v>
+        <v>176.09</v>
       </c>
       <c r="I2" t="n">
         <v>178.3571764034976</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2" t="n">
-        <v>2.94</v>
+        <v>-1.79</v>
       </c>
       <c r="L2" t="n">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="M2" t="n">
         <v>0.54</v>
       </c>
       <c r="N2" t="n">
-        <v>4.07</v>
+        <v>4.59</v>
       </c>
       <c r="O2" t="n">
         <v>0.07000000000000001</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>15.19</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42153</v>
+        <v>42156</v>
       </c>
       <c r="H3" t="n">
-        <v>167.77</v>
+        <v>169.37</v>
       </c>
       <c r="I3" t="n">
         <v>168.5658389439495</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K3" t="n">
-        <v>4.72</v>
+        <v>3.82</v>
       </c>
       <c r="L3" t="n">
         <v>6.67</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>10.9</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42227</v>
+        <v>42228</v>
       </c>
       <c r="H4" t="n">
-        <v>178.03</v>
+        <v>173.26</v>
       </c>
       <c r="I4" t="n">
         <v>175.3037927748255</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K4" t="n">
-        <v>5.11</v>
+        <v>2.3</v>
       </c>
       <c r="L4" t="n">
         <v>6.26</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>13.16</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42445</v>
+        <v>42446</v>
       </c>
       <c r="H5" t="n">
-        <v>70.93000000000001</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="I5" t="n">
         <v>72.75290959690842</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K5" t="n">
-        <v>59.06</v>
+        <v>57.33</v>
       </c>
       <c r="L5" t="n">
         <v>2.35</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>147</v>
+        <v>148</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>8</v>
+      </c>
+      <c r="U5" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>14.53</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42510</v>
+        <v>42513</v>
       </c>
       <c r="H6" t="n">
-        <v>79.53</v>
+        <v>79.17</v>
       </c>
       <c r="I6" t="n">
         <v>79.24869835225482</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K6" t="n">
-        <v>7.57</v>
+        <v>7.09</v>
       </c>
       <c r="L6" t="n">
         <v>3.65</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>9.57</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42515</v>
+        <v>42516</v>
       </c>
       <c r="H7" t="n">
-        <v>81.7</v>
+        <v>85.73</v>
       </c>
       <c r="I7" t="n">
         <v>85.3492826527572</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.2</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>3.61</v>
+        <v>8.84</v>
       </c>
       <c r="M7" t="n">
         <v>1.15</v>
       </c>
       <c r="N7" t="n">
-        <v>4.12</v>
+        <v>4.93</v>
       </c>
       <c r="O7" t="n">
         <v>-0.45</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>11.13</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42584</v>
+        <v>42585</v>
       </c>
       <c r="H8" t="n">
-        <v>92.43000000000001</v>
+        <v>88.87</v>
       </c>
       <c r="I8" t="n">
         <v>90.32772535455479</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K8" t="n">
-        <v>7.82</v>
+        <v>3.66</v>
       </c>
       <c r="L8" t="n">
         <v>11.55</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>13.41</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42619</v>
+        <v>42620</v>
       </c>
       <c r="H9" t="n">
-        <v>92.09999999999999</v>
+        <v>106.43</v>
       </c>
       <c r="I9" t="n">
         <v>98.73951225332661</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.63</v>
+        <v>-19.76</v>
       </c>
       <c r="L9" t="n">
-        <v>9.82</v>
+        <v>21.19</v>
       </c>
       <c r="M9" t="n">
         <v>1.29</v>
       </c>
       <c r="N9" t="n">
-        <v>2.99</v>
+        <v>15.56</v>
       </c>
       <c r="O9" t="n">
         <v>-3.85</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>19.42</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42641</v>
+        <v>42642</v>
       </c>
       <c r="H10" t="n">
-        <v>95.93000000000001</v>
+        <v>88.67</v>
       </c>
       <c r="I10" t="n">
         <v>92.12205056732491</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K10" t="n">
-        <v>-9.869999999999999</v>
+        <v>-16.69</v>
       </c>
       <c r="L10" t="n">
-        <v>16.03</v>
+        <v>18.82</v>
       </c>
       <c r="M10" t="n">
         <v>2.31</v>
       </c>
       <c r="N10" t="n">
-        <v>4.26</v>
+        <v>7.57</v>
       </c>
       <c r="O10" t="n">
         <v>15.56</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>17.05</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42738</v>
+        <v>42739</v>
       </c>
       <c r="H11" t="n">
-        <v>83.2</v>
+        <v>84.73</v>
       </c>
       <c r="I11" t="n">
         <v>84.02860201865761</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K11" t="n">
-        <v>6.17</v>
+        <v>4.44</v>
       </c>
       <c r="L11" t="n">
         <v>10.38</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>7.13</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42873</v>
+        <v>42874</v>
       </c>
       <c r="H12" t="n">
-        <v>109.6</v>
+        <v>109.37</v>
       </c>
       <c r="I12" t="n">
         <v>109.5176306461028</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K12" t="n">
-        <v>29.35</v>
+        <v>29.08</v>
       </c>
       <c r="L12" t="n">
         <v>1.61</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>8.9</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42934</v>
+        <v>42935</v>
       </c>
       <c r="H13" t="n">
-        <v>95.5</v>
+        <v>96.8</v>
       </c>
       <c r="I13" t="n">
         <v>95.76833697067605</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K13" t="n">
-        <v>12.68</v>
+        <v>11.49</v>
       </c>
       <c r="L13" t="n">
         <v>2.4</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>6.6</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42950</v>
+        <v>42951</v>
       </c>
       <c r="H14" t="n">
-        <v>92.43000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="I14" t="n">
         <v>91.52398066201523</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.51</v>
+        <v>-5.48</v>
       </c>
       <c r="L14" t="n">
-        <v>4.96</v>
+        <v>6.33</v>
       </c>
       <c r="M14" t="n">
         <v>0.21</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>7.15</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42991</v>
+        <v>42992</v>
       </c>
       <c r="H15" t="n">
-        <v>88.23</v>
+        <v>91.23</v>
       </c>
       <c r="I15" t="n">
         <v>90.93540683893825</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K15" t="n">
-        <v>3.57</v>
+        <v>0.3</v>
       </c>
       <c r="L15" t="n">
-        <v>2.15</v>
+        <v>6.26</v>
       </c>
       <c r="M15" t="n">
         <v>2.24</v>
       </c>
       <c r="N15" t="n">
-        <v>2.76</v>
+        <v>3.4</v>
       </c>
       <c r="O15" t="n">
         <v>-1.01</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>7.05</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43004</v>
+        <v>43005</v>
       </c>
       <c r="H16" t="n">
-        <v>85.17</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I16" t="n">
         <v>84.79508881743563</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K16" t="n">
-        <v>-6.64</v>
+        <v>-8.91</v>
       </c>
       <c r="L16" t="n">
-        <v>7.85</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="M16" t="n">
         <v>1.46</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>10.74</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43032</v>
+        <v>43033</v>
       </c>
       <c r="H17" t="n">
-        <v>88.2</v>
+        <v>90.7</v>
       </c>
       <c r="I17" t="n">
         <v>90.02393634701787</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K17" t="n">
-        <v>-6.14</v>
+        <v>-9.15</v>
       </c>
       <c r="L17" t="n">
-        <v>6.98</v>
+        <v>10.41</v>
       </c>
       <c r="M17" t="n">
         <v>1.63</v>
       </c>
       <c r="N17" t="n">
-        <v>2.36</v>
+        <v>2.83</v>
       </c>
       <c r="O17" t="n">
         <v>-2.43</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>8.76</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43049</v>
+        <v>43052</v>
       </c>
       <c r="H18" t="n">
-        <v>92.5</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I18" t="n">
         <v>89.50381504101559</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K18" t="n">
-        <v>1.98</v>
+        <v>-1.43</v>
       </c>
       <c r="L18" t="n">
         <v>2.59</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>13.82</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43101</v>
+        <v>43102</v>
       </c>
       <c r="H19" t="n">
-        <v>95.15000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="I19" t="n">
         <v>96.0084457124393</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K19" t="n">
-        <v>-6.43</v>
+        <v>-9.84</v>
       </c>
       <c r="L19" t="n">
-        <v>7.83</v>
+        <v>10.4</v>
       </c>
       <c r="M19" t="n">
         <v>2.45</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>9.390000000000001</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43132</v>
+        <v>43133</v>
       </c>
       <c r="H20" t="n">
-        <v>100.35</v>
+        <v>93.5</v>
       </c>
       <c r="I20" t="n">
         <v>95.59536969257404</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K20" t="n">
-        <v>2.19</v>
+        <v>-4.79</v>
       </c>
       <c r="L20" t="n">
-        <v>4.07</v>
+        <v>6.77</v>
       </c>
       <c r="M20" t="n">
-        <v>0.71</v>
+        <v>1.2</v>
       </c>
       <c r="N20" t="n">
-        <v>2.45</v>
+        <v>6.83</v>
       </c>
       <c r="O20" t="n">
         <v>3.21</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>16.3</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43196</v>
+        <v>43199</v>
       </c>
       <c r="H21" t="n">
-        <v>87.59999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="I21" t="n">
         <v>88.48932314867113</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K21" t="n">
-        <v>6.31</v>
+        <v>5.35</v>
       </c>
       <c r="L21" t="n">
         <v>6.15</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>8.130000000000001</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43227</v>
+        <v>43228</v>
       </c>
       <c r="H22" t="n">
-        <v>84.34999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="I22" t="n">
         <v>83.72348064058841</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.69</v>
+        <v>-5.88</v>
       </c>
       <c r="L22" t="n">
-        <v>5.76</v>
+        <v>6.61</v>
       </c>
       <c r="M22" t="n">
         <v>0.97</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>8.17</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43248</v>
+        <v>43249</v>
       </c>
       <c r="H23" t="n">
-        <v>79.25</v>
+        <v>83.45</v>
       </c>
       <c r="I23" t="n">
         <v>81.85717951084308</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K23" t="n">
-        <v>4.86</v>
+        <v>-0.18</v>
       </c>
       <c r="L23" t="n">
-        <v>1.92</v>
+        <v>4.26</v>
       </c>
       <c r="M23" t="n">
         <v>0.84</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>11.06</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43255</v>
+        <v>43256</v>
       </c>
       <c r="H24" t="n">
-        <v>75.25</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="I24" t="n">
         <v>74.21818459621709</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K24" t="n">
-        <v>-9.83</v>
+        <v>-12.34</v>
       </c>
       <c r="L24" t="n">
-        <v>10.49</v>
+        <v>12.94</v>
       </c>
       <c r="M24" t="n">
         <v>2.1</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>15.33</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43304</v>
+        <v>43305</v>
       </c>
       <c r="H25" t="n">
-        <v>69.5</v>
+        <v>73.45</v>
       </c>
       <c r="I25" t="n">
         <v>73.01856525122366</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K25" t="n">
-        <v>4.99</v>
+        <v>-0.41</v>
       </c>
       <c r="L25" t="n">
         <v>8.68</v>
@@ -1866,7 +2165,7 @@
         <v>1.86</v>
       </c>
       <c r="N25" t="n">
-        <v>4.69</v>
+        <v>5.68</v>
       </c>
       <c r="O25" t="n">
         <v>-2.79</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>13.84</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43362</v>
+        <v>43364</v>
       </c>
       <c r="H26" t="n">
-        <v>74.84999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="I26" t="n">
         <v>73.22077004942352</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K26" t="n">
-        <v>1.91</v>
+        <v>-2.65</v>
       </c>
       <c r="L26" t="n">
-        <v>5.65</v>
+        <v>8.1</v>
       </c>
       <c r="M26" t="n">
         <v>0.55</v>
       </c>
       <c r="N26" t="n">
-        <v>3.73</v>
+        <v>4.48</v>
       </c>
       <c r="O26" t="n">
         <v>5.68</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>15.15</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43461</v>
+        <v>43462</v>
       </c>
       <c r="H27" t="n">
-        <v>70</v>
+        <v>72.05</v>
       </c>
       <c r="I27" t="n">
         <v>71.71188672266605</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K27" t="n">
-        <v>2.1</v>
+        <v>-0.77</v>
       </c>
       <c r="L27" t="n">
         <v>8.6</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>5</v>
+      </c>
+      <c r="U27" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>11.49</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43489</v>
+        <v>43490</v>
       </c>
       <c r="H28" t="n">
-        <v>69.05</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I28" t="n">
         <v>66.82356028969825</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K28" t="n">
-        <v>-4.16</v>
+        <v>-7.84</v>
       </c>
       <c r="L28" t="n">
-        <v>6.32</v>
+        <v>8.33</v>
       </c>
       <c r="M28" t="n">
         <v>0.54</v>
       </c>
       <c r="N28" t="n">
-        <v>3.08</v>
+        <v>3.84</v>
       </c>
       <c r="O28" t="n">
         <v>2.93</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>10.96</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43529</v>
+        <v>43530</v>
       </c>
       <c r="H29" t="n">
-        <v>67.3</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I29" t="n">
         <v>67.54850972851608</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.36</v>
+        <v>-4.07</v>
       </c>
       <c r="L29" t="n">
-        <v>4.67</v>
+        <v>5.65</v>
       </c>
       <c r="M29" t="n">
         <v>2.42</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>8.91</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43585</v>
+        <v>43587</v>
       </c>
       <c r="H30" t="n">
-        <v>70.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I30" t="n">
         <v>69.66561115592869</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K30" t="n">
-        <v>2.46</v>
+        <v>0.72</v>
       </c>
       <c r="L30" t="n">
         <v>4.34</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>12.26</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43608</v>
+        <v>43609</v>
       </c>
       <c r="H31" t="n">
-        <v>66.55</v>
+        <v>69</v>
       </c>
       <c r="I31" t="n">
         <v>68.75237700665116</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K31" t="n">
-        <v>4.38</v>
+        <v>0.86</v>
       </c>
       <c r="L31" t="n">
         <v>2.95</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>15.01</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43651</v>
+        <v>43654</v>
       </c>
       <c r="H32" t="n">
-        <v>70.15000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="I32" t="n">
         <v>67.690684152892</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K32" t="n">
-        <v>1.67</v>
+        <v>-2.46</v>
       </c>
       <c r="L32" t="n">
         <v>3.77</v>
       </c>
       <c r="M32" t="n">
-        <v>0.57</v>
+        <v>0.93</v>
       </c>
       <c r="N32" t="n">
-        <v>4.04</v>
+        <v>4.06</v>
       </c>
       <c r="O32" t="n">
         <v>3.68</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>12.84</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43755</v>
+        <v>43756</v>
       </c>
       <c r="H33" t="n">
-        <v>44.6</v>
+        <v>54.35</v>
       </c>
       <c r="I33" t="n">
         <v>48.36349328510421</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K33" t="n">
-        <v>33.73</v>
+        <v>19.24</v>
       </c>
       <c r="L33" t="n">
         <v>4.53</v>
       </c>
       <c r="M33" t="n">
-        <v>2.89</v>
+        <v>9.98</v>
       </c>
       <c r="N33" t="n">
-        <v>6.57</v>
+        <v>21.86</v>
       </c>
       <c r="O33" t="n">
         <v>-4.06</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>19.7</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43803</v>
+        <v>43804</v>
       </c>
       <c r="H34" t="n">
-        <v>49.95</v>
+        <v>48.75</v>
       </c>
       <c r="I34" t="n">
         <v>49.1401486357617</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K34" t="n">
-        <v>-8.1</v>
+        <v>-10.3</v>
       </c>
       <c r="L34" t="n">
-        <v>10.21</v>
+        <v>10.76</v>
       </c>
       <c r="M34" t="n">
         <v>2.8</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>14.83</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43963</v>
+        <v>43964</v>
       </c>
       <c r="H35" t="n">
-        <v>21.5</v>
+        <v>26.6</v>
       </c>
       <c r="I35" t="n">
         <v>24.25335671243906</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K35" t="n">
-        <v>55.9</v>
+        <v>45.44</v>
       </c>
       <c r="L35" t="n">
         <v>2.97</v>
       </c>
       <c r="M35" t="n">
-        <v>4.89</v>
+        <v>7.44</v>
       </c>
       <c r="N35" t="n">
-        <v>7.45</v>
+        <v>23.72</v>
       </c>
       <c r="O35" t="n">
         <v>-2.4</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>6</v>
+      </c>
+      <c r="U35" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>26.87</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44048</v>
+        <v>44049</v>
       </c>
       <c r="H36" t="n">
-        <v>36.7</v>
+        <v>35.7</v>
       </c>
       <c r="I36" t="n">
         <v>35.75752876078434</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K36" t="n">
-        <v>37.97</v>
+        <v>34.21</v>
       </c>
       <c r="L36" t="n">
         <v>16.73</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,25 +2972,25 @@
         <v>15.55</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44063</v>
+        <v>44064</v>
       </c>
       <c r="H37" t="n">
-        <v>38.5</v>
+        <v>40.65</v>
       </c>
       <c r="I37" t="n">
         <v>39.91519578440551</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K37" t="n">
-        <v>-7.84</v>
+        <v>-13.87</v>
       </c>
       <c r="L37" t="n">
-        <v>11.2</v>
+        <v>17.51</v>
       </c>
       <c r="M37" t="n">
-        <v>2.13</v>
+        <v>2.47</v>
       </c>
       <c r="N37" t="n">
         <v>8.039999999999999</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>14.09</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44089</v>
+        <v>44090</v>
       </c>
       <c r="H38" t="n">
-        <v>35.95</v>
+        <v>35.65</v>
       </c>
       <c r="I38" t="n">
         <v>35.91124840813315</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K38" t="n">
-        <v>-11.56</v>
+        <v>-12.3</v>
       </c>
       <c r="L38" t="n">
-        <v>12.42</v>
+        <v>12.55</v>
       </c>
       <c r="M38" t="n">
         <v>2.62</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>13.14</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44155</v>
+        <v>44158</v>
       </c>
       <c r="H39" t="n">
-        <v>29.2</v>
+        <v>31.35</v>
       </c>
       <c r="I39" t="n">
         <v>30.26685018750867</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K39" t="n">
-        <v>18.09</v>
+        <v>12.06</v>
       </c>
       <c r="L39" t="n">
         <v>1.4</v>
@@ -2664,7 +3131,7 @@
         <v>2.32</v>
       </c>
       <c r="N39" t="n">
-        <v>5.47</v>
+        <v>7.36</v>
       </c>
       <c r="O39" t="n">
         <v>-0.83</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>13.81</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44183</v>
+        <v>44186</v>
       </c>
       <c r="H40" t="n">
-        <v>35.85</v>
+        <v>32.55</v>
       </c>
       <c r="I40" t="n">
         <v>32.65692235342122</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K40" t="n">
-        <v>14.35</v>
+        <v>3.83</v>
       </c>
       <c r="L40" t="n">
         <v>6.7</v>
       </c>
       <c r="M40" t="n">
-        <v>0.41</v>
+        <v>0.98</v>
       </c>
       <c r="N40" t="n">
-        <v>2.6</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="O40" t="n">
         <v>7.36</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>19.01</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44196</v>
+        <v>44197</v>
       </c>
       <c r="H41" t="n">
-        <v>35.9</v>
+        <v>38.7</v>
       </c>
       <c r="I41" t="n">
         <v>37.11465077250252</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K41" t="n">
-        <v>-10.29</v>
+        <v>-18.89</v>
       </c>
       <c r="L41" t="n">
-        <v>12.14</v>
+        <v>19.82</v>
       </c>
       <c r="M41" t="n">
         <v>1.98</v>
       </c>
       <c r="N41" t="n">
-        <v>4.29</v>
+        <v>7.8</v>
       </c>
       <c r="O41" t="n">
         <v>-9.210000000000001</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>16.52</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44295</v>
+        <v>44298</v>
       </c>
       <c r="H42" t="n">
-        <v>51.5</v>
+        <v>45.05</v>
       </c>
       <c r="I42" t="n">
         <v>45.74520722513213</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K42" t="n">
-        <v>33.07</v>
+        <v>16.41</v>
       </c>
       <c r="L42" t="n">
         <v>9.300000000000001</v>
@@ -2835,7 +3338,7 @@
         <v>5.28</v>
       </c>
       <c r="N42" t="n">
-        <v>8.5</v>
+        <v>12.52</v>
       </c>
       <c r="O42" t="n">
         <v>7.8</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>23.57</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44316</v>
+        <v>44319</v>
       </c>
       <c r="H43" t="n">
-        <v>48.3</v>
+        <v>53.5</v>
       </c>
       <c r="I43" t="n">
         <v>51.42426864538152</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K43" t="n">
-        <v>-7.21</v>
+        <v>-18.76</v>
       </c>
       <c r="L43" t="n">
-        <v>10.99</v>
+        <v>22.42</v>
       </c>
       <c r="M43" t="n">
         <v>1.93</v>
       </c>
       <c r="N43" t="n">
-        <v>4.66</v>
+        <v>10.77</v>
       </c>
       <c r="O43" t="n">
         <v>-12.52</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>19.69</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44363</v>
+        <v>44364</v>
       </c>
       <c r="H44" t="n">
-        <v>67</v>
+        <v>65.5</v>
       </c>
       <c r="I44" t="n">
         <v>66.48697554003495</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K44" t="n">
-        <v>25.23</v>
+        <v>22.43</v>
       </c>
       <c r="L44" t="n">
         <v>11.4</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>20.99</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44466</v>
+        <v>44467</v>
       </c>
       <c r="H45" t="n">
-        <v>56.95</v>
+        <v>60.35</v>
       </c>
       <c r="I45" t="n">
         <v>58.64329631194409</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K45" t="n">
-        <v>13.05</v>
+        <v>7.86</v>
       </c>
       <c r="L45" t="n">
         <v>5.88</v>
@@ -3006,7 +3545,7 @@
         <v>3.71</v>
       </c>
       <c r="N45" t="n">
-        <v>5.45</v>
+        <v>5.97</v>
       </c>
       <c r="O45" t="n">
         <v>-2.24</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>14.05</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44510</v>
+        <v>44511</v>
       </c>
       <c r="H46" t="n">
-        <v>66.25</v>
+        <v>64.8</v>
       </c>
       <c r="I46" t="n">
         <v>65.0214369139532</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K46" t="n">
-        <v>9.779999999999999</v>
+        <v>7.37</v>
       </c>
       <c r="L46" t="n">
         <v>5.8</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>17.33</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44574</v>
+        <v>44575</v>
       </c>
       <c r="H47" t="n">
-        <v>62.7</v>
+        <v>63.7</v>
       </c>
       <c r="I47" t="n">
         <v>63.52436612173392</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K47" t="n">
-        <v>3.24</v>
+        <v>1.7</v>
       </c>
       <c r="L47" t="n">
         <v>3.55</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>10.37</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H48" t="n">
-        <v>59.6</v>
+        <v>57.25</v>
       </c>
       <c r="I48" t="n">
         <v>58.17282696990739</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K48" t="n">
-        <v>-6.44</v>
+        <v>-10.13</v>
       </c>
       <c r="L48" t="n">
-        <v>8.08</v>
+        <v>11.62</v>
       </c>
       <c r="M48" t="n">
         <v>0.49</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>14.05</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44651</v>
+        <v>44652</v>
       </c>
       <c r="H49" t="n">
-        <v>49.35</v>
+        <v>53.85</v>
       </c>
       <c r="I49" t="n">
         <v>53.61418870729707</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K49" t="n">
-        <v>13.8</v>
+        <v>5.94</v>
       </c>
       <c r="L49" t="n">
         <v>7.86</v>
@@ -3234,7 +3821,7 @@
         <v>7.33</v>
       </c>
       <c r="N49" t="n">
-        <v>8.57</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="O49" t="n">
         <v>-3.94</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>14.7</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44686</v>
+        <v>44687</v>
       </c>
       <c r="H50" t="n">
-        <v>53.85</v>
+        <v>51.05</v>
       </c>
       <c r="I50" t="n">
         <v>51.44122395086923</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>-5.2</v>
       </c>
       <c r="L50" t="n">
         <v>8.17</v>
       </c>
       <c r="M50" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="N50" t="n">
-        <v>4.17</v>
+        <v>5.2</v>
       </c>
       <c r="O50" t="n">
         <v>9.119999999999999</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>14.08</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44700</v>
+        <v>44701</v>
       </c>
       <c r="H51" t="n">
-        <v>49.35</v>
+        <v>53.1</v>
       </c>
       <c r="I51" t="n">
         <v>52.50743786447874</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K51" t="n">
-        <v>3.33</v>
+        <v>-4.02</v>
       </c>
       <c r="L51" t="n">
-        <v>3.72</v>
+        <v>4.8</v>
       </c>
       <c r="M51" t="n">
         <v>2.57</v>
       </c>
       <c r="N51" t="n">
-        <v>5.08</v>
+        <v>7.6</v>
       </c>
       <c r="O51" t="n">
         <v>-5.2</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>15.94</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44727</v>
+        <v>44728</v>
       </c>
       <c r="H52" t="n">
-        <v>47.5</v>
+        <v>45.6</v>
       </c>
       <c r="I52" t="n">
         <v>46.20040564974576</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K52" t="n">
-        <v>-10.55</v>
+        <v>-14.12</v>
       </c>
       <c r="L52" t="n">
-        <v>11.3</v>
+        <v>14.69</v>
       </c>
       <c r="M52" t="n">
         <v>1.61</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>13.9</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44755</v>
+        <v>44756</v>
       </c>
       <c r="H53" t="n">
-        <v>48.35</v>
+        <v>49.25</v>
       </c>
       <c r="I53" t="n">
         <v>49.08815849301331</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K53" t="n">
-        <v>-6.03</v>
+        <v>-8</v>
       </c>
       <c r="L53" t="n">
         <v>8.99</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>9.640000000000001</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H54" t="n">
-        <v>58</v>
+        <v>55.35</v>
       </c>
       <c r="I54" t="n">
         <v>57.95492093664456</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K54" t="n">
-        <v>17.77</v>
+        <v>12.39</v>
       </c>
       <c r="L54" t="n">
         <v>2.13</v>
@@ -3519,7 +4166,7 @@
         <v>3.2</v>
       </c>
       <c r="N54" t="n">
-        <v>3.74</v>
+        <v>4.57</v>
       </c>
       <c r="O54" t="n">
         <v>1.86</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,25 +4214,25 @@
         <v>13.25</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44837</v>
+        <v>44838</v>
       </c>
       <c r="H55" t="n">
-        <v>60.55</v>
+        <v>62</v>
       </c>
       <c r="I55" t="n">
         <v>61.67090689015966</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K55" t="n">
-        <v>-9.390000000000001</v>
+        <v>-12.01</v>
       </c>
       <c r="L55" t="n">
-        <v>11.65</v>
+        <v>12.74</v>
       </c>
       <c r="M55" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="N55" t="n">
         <v>2.54</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>10.16</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44916</v>
+        <v>44917</v>
       </c>
       <c r="H56" t="n">
-        <v>81.15000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I56" t="n">
         <v>79.41793113567556</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K56" t="n">
-        <v>30.89</v>
+        <v>27.26</v>
       </c>
       <c r="L56" t="n">
         <v>3.15</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>15.11</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>44986</v>
+        <v>44987</v>
       </c>
       <c r="H57" t="n">
-        <v>72.8</v>
+        <v>74.8</v>
       </c>
       <c r="I57" t="n">
         <v>74.62061921816732</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K57" t="n">
-        <v>7.73</v>
+        <v>5.2</v>
       </c>
       <c r="L57" t="n">
         <v>5.83</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>4</v>
+      </c>
+      <c r="U57" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>11.52</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45012</v>
+        <v>45013</v>
       </c>
       <c r="H58" t="n">
-        <v>71.05</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="I58" t="n">
         <v>70.81024661187014</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K58" t="n">
-        <v>-5.01</v>
+        <v>-6.28</v>
       </c>
       <c r="L58" t="n">
-        <v>5.55</v>
+        <v>6.95</v>
       </c>
       <c r="M58" t="n">
         <v>1.81</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>10.04</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45035</v>
+        <v>45036</v>
       </c>
       <c r="H59" t="n">
-        <v>75.40000000000001</v>
+        <v>76.25</v>
       </c>
       <c r="I59" t="n">
         <v>75.4740616375847</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K59" t="n">
-        <v>-7.56</v>
+        <v>-8.77</v>
       </c>
       <c r="L59" t="n">
         <v>9.77</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,25 +4559,25 @@
         <v>8.66</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45142</v>
+        <v>45145</v>
       </c>
       <c r="H60" t="n">
-        <v>98.95</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I60" t="n">
         <v>97.04392563628264</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K60" t="n">
-        <v>29.77</v>
+        <v>26.69</v>
       </c>
       <c r="L60" t="n">
         <v>2.1</v>
       </c>
       <c r="M60" t="n">
-        <v>1.81</v>
+        <v>3.54</v>
       </c>
       <c r="N60" t="n">
         <v>6.16</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>5</v>
+      </c>
+      <c r="U60" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>11.47</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45159</v>
+        <v>45160</v>
       </c>
       <c r="H61" t="n">
-        <v>100.95</v>
+        <v>111.05</v>
       </c>
       <c r="I61" t="n">
         <v>107.6776453900349</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K61" t="n">
-        <v>-4.5</v>
+        <v>-14.96</v>
       </c>
       <c r="L61" t="n">
-        <v>7.61</v>
+        <v>16.82</v>
       </c>
       <c r="M61" t="n">
         <v>1.09</v>
       </c>
       <c r="N61" t="n">
-        <v>3.2</v>
+        <v>10</v>
       </c>
       <c r="O61" t="n">
         <v>-2.37</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,25 +4697,25 @@
         <v>14.9</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45187</v>
+        <v>45189</v>
       </c>
       <c r="H62" t="n">
-        <v>126.45</v>
+        <v>123.6</v>
       </c>
       <c r="I62" t="n">
         <v>125.3209514977513</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K62" t="n">
-        <v>13.87</v>
+        <v>11.3</v>
       </c>
       <c r="L62" t="n">
         <v>9</v>
       </c>
       <c r="M62" t="n">
-        <v>-0</v>
+        <v>0.36</v>
       </c>
       <c r="N62" t="n">
         <v>10.15</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>17.65</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45242</v>
+        <v>45243</v>
       </c>
       <c r="H63" t="n">
-        <v>129</v>
+        <v>136.5</v>
       </c>
       <c r="I63" t="n">
         <v>130.7121377606369</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K63" t="n">
-        <v>-4.37</v>
+        <v>-10.44</v>
       </c>
       <c r="L63" t="n">
-        <v>8.210000000000001</v>
+        <v>11.65</v>
       </c>
       <c r="M63" t="n">
         <v>1.3</v>
       </c>
       <c r="N63" t="n">
-        <v>5.35</v>
+        <v>5.81</v>
       </c>
       <c r="O63" t="n">
         <v>-2.25</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>12.92</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H64" t="n">
-        <v>244.1</v>
+        <v>225.3</v>
       </c>
       <c r="I64" t="n">
         <v>225.4223987738353</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K64" t="n">
-        <v>78.83</v>
+        <v>65.05</v>
       </c>
       <c r="L64" t="n">
         <v>5.71</v>
@@ -4089,7 +4856,7 @@
         <v>5.09</v>
       </c>
       <c r="N64" t="n">
-        <v>7.65</v>
+        <v>7.7</v>
       </c>
       <c r="O64" t="n">
         <v>5.81</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>5</v>
+      </c>
+      <c r="U64" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>21.77</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45391</v>
+        <v>45392</v>
       </c>
       <c r="H65" t="n">
-        <v>255.75</v>
+        <v>262.5</v>
       </c>
       <c r="I65" t="n">
         <v>258.9412488259107</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K65" t="n">
-        <v>-13.52</v>
+        <v>-16.51</v>
       </c>
       <c r="L65" t="n">
-        <v>15.36</v>
+        <v>17.75</v>
       </c>
       <c r="M65" t="n">
         <v>4.09</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>10.92</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H66" t="n">
-        <v>311.45</v>
+        <v>246.55</v>
       </c>
       <c r="I66" t="n">
         <v>280.042627098584</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K66" t="n">
-        <v>18.65</v>
+        <v>-6.08</v>
       </c>
       <c r="L66" t="n">
-        <v>6.19</v>
+        <v>14.65</v>
       </c>
       <c r="M66" t="n">
         <v>5.39</v>
       </c>
       <c r="N66" t="n">
-        <v>5.4</v>
+        <v>20.84</v>
       </c>
       <c r="O66" t="n">
         <v>2.64</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>32.42</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45456</v>
+        <v>45457</v>
       </c>
       <c r="H67" t="n">
-        <v>303.95</v>
+        <v>305.7</v>
       </c>
       <c r="I67" t="n">
         <v>304.6041515611403</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K67" t="n">
-        <v>-23.28</v>
+        <v>-23.99</v>
       </c>
       <c r="L67" t="n">
         <v>26.16</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>16.82</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45491</v>
+        <v>45492</v>
       </c>
       <c r="H68" t="n">
-        <v>308.6</v>
+        <v>294.1</v>
       </c>
       <c r="I68" t="n">
         <v>296.4555335599354</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K68" t="n">
-        <v>0.95</v>
+        <v>-3.79</v>
       </c>
       <c r="L68" t="n">
         <v>5.63</v>
       </c>
       <c r="M68" t="n">
-        <v>0.36</v>
+        <v>0.86</v>
       </c>
       <c r="N68" t="n">
-        <v>3.56</v>
+        <v>4.7</v>
       </c>
       <c r="O68" t="n">
         <v>0.58</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>14</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45561</v>
+        <v>45562</v>
       </c>
       <c r="H69" t="n">
-        <v>280.65</v>
+        <v>287.55</v>
       </c>
       <c r="I69" t="n">
         <v>283.1174226776351</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K69" t="n">
-        <v>4.57</v>
+        <v>2.23</v>
       </c>
       <c r="L69" t="n">
         <v>11.19</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>4</v>
+      </c>
+      <c r="U69" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45569</v>
+        <v>45572</v>
       </c>
       <c r="H70" t="n">
-        <v>267.6</v>
+        <v>256.65</v>
       </c>
       <c r="I70" t="n">
         <v>262.0857193247749</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K70" t="n">
-        <v>-6.94</v>
+        <v>-10.75</v>
       </c>
       <c r="L70" t="n">
-        <v>8.800000000000001</v>
+        <v>11.62</v>
       </c>
       <c r="M70" t="n">
         <v>2.23</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>13.7</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45623</v>
+        <v>45624</v>
       </c>
       <c r="H71" t="n">
-        <v>247.66</v>
+        <v>252.49</v>
       </c>
       <c r="I71" t="n">
         <v>250.9371285460197</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K71" t="n">
-        <v>3.5</v>
+        <v>1.62</v>
       </c>
       <c r="L71" t="n">
         <v>7.36</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>11.23</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45653</v>
+        <v>45656</v>
       </c>
       <c r="H72" t="n">
-        <v>235.4</v>
+        <v>225.6</v>
       </c>
       <c r="I72" t="n">
         <v>230.8271175747811</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K72" t="n">
-        <v>-6.77</v>
+        <v>-10.65</v>
       </c>
       <c r="L72" t="n">
-        <v>8.119999999999999</v>
+        <v>11.44</v>
       </c>
       <c r="M72" t="n">
         <v>3.09</v>
       </c>
       <c r="N72" t="n">
-        <v>3.63</v>
+        <v>4.16</v>
       </c>
       <c r="O72" t="n">
         <v>1.95</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>12.37</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45736</v>
+        <v>45737</v>
       </c>
       <c r="H73" t="n">
-        <v>206.54</v>
+        <v>211.95</v>
       </c>
       <c r="I73" t="n">
         <v>209.0049237977136</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K73" t="n">
-        <v>8.449999999999999</v>
+        <v>6.05</v>
       </c>
       <c r="L73" t="n">
         <v>4.95</v>
@@ -4611,7 +5486,19 @@
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>3</v>
+      </c>
+      <c r="U73" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>11.08</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45862</v>
+        <v>45863</v>
       </c>
       <c r="H74" t="n">
-        <v>251.05</v>
+        <v>240.15</v>
       </c>
       <c r="I74" t="n">
         <v>247.4436521975671</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K74" t="n">
-        <v>18.45</v>
+        <v>13.31</v>
       </c>
       <c r="L74" t="n">
         <v>8.699999999999999</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>5</v>
+      </c>
+      <c r="U74" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>9.31</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="H75" t="n">
-        <v>220.03</v>
+        <v>229.08</v>
       </c>
       <c r="I75" t="n">
         <v>225.5085648427591</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K75" t="n">
-        <v>8.380000000000001</v>
+        <v>4.61</v>
       </c>
       <c r="L75" t="n">
         <v>4.5</v>
@@ -4725,7 +5624,19 @@
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>3</v>
+      </c>
+      <c r="U75" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>9.92</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="H76" t="n">
-        <v>277.75</v>
+        <v>269.7</v>
       </c>
       <c r="I76" t="n">
         <v>272.6463069035347</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K76" t="n">
-        <v>21.25</v>
+        <v>17.73</v>
       </c>
       <c r="L76" t="n">
         <v>4.22</v>
@@ -4773,7 +5684,7 @@
         <v>0.93</v>
       </c>
       <c r="N76" t="n">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="O76" t="n">
         <v>4.11</v>
@@ -4782,7 +5693,19 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>4</v>
+      </c>
+      <c r="U76" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="77">
@@ -4809,25 +5732,25 @@
         <v>9.619999999999999</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="H77" t="n">
-        <v>291.45</v>
+        <v>299.5</v>
       </c>
       <c r="I77" t="n">
         <v>295.6367787365318</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K77" t="n">
-        <v>-8.06</v>
+        <v>-11.05</v>
       </c>
       <c r="L77" t="n">
-        <v>8.75</v>
+        <v>11.55</v>
       </c>
       <c r="M77" t="n">
-        <v>0.37</v>
+        <v>0.43</v>
       </c>
       <c r="N77" t="n">
         <v>3.13</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,28 +5801,28 @@
         <v>8.32</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="H78" t="n">
-        <v>303.55</v>
+        <v>271.75</v>
       </c>
       <c r="I78" t="n">
         <v>278.6620758114811</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K78" t="n">
-        <v>1.35</v>
+        <v>-9.27</v>
       </c>
       <c r="L78" t="n">
-        <v>2.65</v>
+        <v>12.69</v>
       </c>
       <c r="M78" t="n">
         <v>-0</v>
       </c>
       <c r="N78" t="n">
-        <v>1.03</v>
+        <v>10.48</v>
       </c>
       <c r="O78" t="n">
         <v>2.76</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S78" t="b">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4923,19 +5870,19 @@
         <v>16.17</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="H79" t="n">
-        <v>265.7</v>
+        <v>277.2</v>
       </c>
       <c r="I79" t="n">
         <v>275.620624831732</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K79" t="n">
-        <v>2.23</v>
+        <v>-2.01</v>
       </c>
       <c r="L79" t="n">
         <v>11.83</v>
@@ -4953,7 +5900,19 @@
         <v>1</v>
       </c>
       <c r="Q79" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>4</v>
+      </c>
+      <c r="U79" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -4980,19 +5939,19 @@
         <v>14.19</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H80" t="n">
-        <v>396.55</v>
+        <v>377.3</v>
       </c>
       <c r="I80" t="n">
         <v>383.3945230742288</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K80" t="n">
-        <v>43.06</v>
+        <v>36.11</v>
       </c>
       <c r="L80" t="n">
         <v>4.85</v>
@@ -5001,7 +5960,7 @@
         <v>2.31</v>
       </c>
       <c r="N80" t="n">
-        <v>4.21</v>
+        <v>4.85</v>
       </c>
       <c r="O80" t="n">
         <v>4.33</v>
@@ -5010,7 +5969,19 @@
         <v>1</v>
       </c>
       <c r="Q80" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>3</v>
+      </c>
+      <c r="U80" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -5037,22 +6008,22 @@
         <v>14.28</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="H81" t="n">
-        <v>403.9</v>
+        <v>417.95</v>
       </c>
       <c r="I81" t="n">
         <v>417.3646819561494</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K81" t="n">
-        <v>-7.05</v>
+        <v>-10.77</v>
       </c>
       <c r="L81" t="n">
-        <v>12.3</v>
+        <v>12.38</v>
       </c>
       <c r="M81" t="n">
         <v>2.41</v>
@@ -5067,7 +6038,19 @@
         <v>1</v>
       </c>
       <c r="Q81" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>2</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -5094,19 +6077,19 @@
         <v>11.61</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="H82" t="n">
-        <v>427.35</v>
+        <v>410.2</v>
       </c>
       <c r="I82" t="n">
         <v>411.0717206348102</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K82" t="n">
-        <v>2.25</v>
+        <v>-1.85</v>
       </c>
       <c r="L82" t="n">
         <v>5.37</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>4</v>
+      </c>
+      <c r="U82" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -5175,6 +6170,14 @@
       <c r="Q83" t="n">
         <v>6</v>
       </c>
+      <c r="R83" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S83" t="b">
+        <v>1</v>
+      </c>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10133,7 +11136,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>51.6</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
@@ -10143,7 +11146,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -10153,7 +11156,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8">
@@ -10163,7 +11166,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -10173,7 +11176,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -10183,7 +11186,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11">
@@ -10193,7 +11196,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
@@ -10203,7 +11206,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -10213,7 +11216,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>40.7</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="14">
@@ -10223,7 +11226,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.42</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="15">
@@ -10233,7 +11236,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8.91</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="16">
@@ -10243,7 +11246,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.87</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="17">
@@ -10253,7 +11256,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>78.83</v>
+        <v>65.05</v>
       </c>
     </row>
     <row r="18">
@@ -10263,7 +11266,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>61.7</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="19">
@@ -10273,7 +11276,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.19</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="20">
@@ -10283,7 +11286,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.32</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="21">
@@ -10303,7 +11306,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23">
@@ -10313,7 +11316,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24">
@@ -10323,7 +11326,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.54</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="25">
@@ -10333,7 +11336,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9.539999999999999</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="26">
@@ -10343,7 +11346,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.01</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="27">
@@ -10353,7 +11356,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>11.55</v>
+        <v>23.72</v>
       </c>
     </row>
     <row r="28">
@@ -10363,7 +11366,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29">
